--- a/modeleLogiqueEntete/ig/StructureDefinition-fr-cda-hors-amm.xlsx
+++ b/modeleLogiqueEntete/ig/StructureDefinition-fr-cda-hors-amm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T09:13:27+00:00</t>
+    <t>2026-06-09T09:28:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/modeleLogiqueEntete/ig/StructureDefinition-fr-cda-hors-amm.xlsx
+++ b/modeleLogiqueEntete/ig/StructureDefinition-fr-cda-hors-amm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T09:28:52+00:00</t>
+    <t>2026-06-09T14:42:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/modeleLogiqueEntete/ig/StructureDefinition-fr-cda-hors-amm.xlsx
+++ b/modeleLogiqueEntete/ig/StructureDefinition-fr-cda-hors-amm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T14:42:35+00:00</t>
+    <t>2026-06-15T15:31:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
